--- a/artfynd/A 54650-2022 artfynd.xlsx
+++ b/artfynd/A 54650-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54650-2022 artfynd.xlsx
+++ b/artfynd/A 54650-2022 artfynd.xlsx
@@ -794,12 +794,7 @@
         <v>2762594</v>
       </c>
       <c r="B3" t="n">
-        <v>106963</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>393108.8964390595</v>
+        <v>393109</v>
       </c>
       <c r="R3" t="n">
-        <v>6353490.013974749</v>
+        <v>6353490</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -864,19 +859,9 @@
           <t>1983-05-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1983-05-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54650-2022 artfynd.xlsx
+++ b/artfynd/A 54650-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>3191643</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>393108.8964390595</v>
+        <v>393109</v>
       </c>
       <c r="R2" t="n">
-        <v>6353490.013974749</v>
+        <v>6353490</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1983-05-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1983-05-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -895,12 +880,7 @@
         <v>2330905</v>
       </c>
       <c r="B4" t="n">
-        <v>104837</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>393108.8964390595</v>
+        <v>393109</v>
       </c>
       <c r="R4" t="n">
-        <v>6353490.013974749</v>
+        <v>6353490</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -965,19 +945,9 @@
           <t>1983-05-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1983-05-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,12 +981,7 @@
         <v>4690495</v>
       </c>
       <c r="B5" t="n">
-        <v>96925</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>393108.8964390595</v>
+        <v>393109</v>
       </c>
       <c r="R5" t="n">
-        <v>6353490.013974749</v>
+        <v>6353490</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1081,19 +1046,9 @@
           <t>1983-05-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1983-05-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54650-2022 artfynd.xlsx
+++ b/artfynd/A 54650-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3191643</v>
       </c>
       <c r="B2" t="n">
-        <v>106169</v>
+        <v>106181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2762594</v>
       </c>
       <c r="B3" t="n">
-        <v>109398</v>
+        <v>109413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2330905</v>
       </c>
       <c r="B4" t="n">
-        <v>107248</v>
+        <v>107262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4690495</v>
       </c>
       <c r="B5" t="n">
-        <v>99198</v>
+        <v>99206</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54650-2022 artfynd.xlsx
+++ b/artfynd/A 54650-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3191643</v>
       </c>
       <c r="B2" t="n">
-        <v>106181</v>
+        <v>106190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2762594</v>
       </c>
       <c r="B3" t="n">
-        <v>109413</v>
+        <v>109422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2330905</v>
       </c>
       <c r="B4" t="n">
-        <v>107262</v>
+        <v>107271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4690495</v>
       </c>
       <c r="B5" t="n">
-        <v>99206</v>
+        <v>99212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54650-2022 artfynd.xlsx
+++ b/artfynd/A 54650-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3191643</v>
       </c>
       <c r="B2" t="n">
-        <v>106190</v>
+        <v>106202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2762594</v>
       </c>
       <c r="B3" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2330905</v>
       </c>
       <c r="B4" t="n">
-        <v>107271</v>
+        <v>107283</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4690495</v>
       </c>
       <c r="B5" t="n">
-        <v>99212</v>
+        <v>99215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54650-2022 artfynd.xlsx
+++ b/artfynd/A 54650-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3191643</v>
       </c>
       <c r="B2" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2762594</v>
       </c>
       <c r="B3" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2330905</v>
       </c>
       <c r="B4" t="n">
-        <v>107283</v>
+        <v>107292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4690495</v>
       </c>
       <c r="B5" t="n">
-        <v>99215</v>
+        <v>99220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54650-2022 artfynd.xlsx
+++ b/artfynd/A 54650-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3191643</v>
       </c>
       <c r="B2" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2762594</v>
       </c>
       <c r="B3" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2330905</v>
       </c>
       <c r="B4" t="n">
-        <v>107292</v>
+        <v>107297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4690495</v>
       </c>
       <c r="B5" t="n">
-        <v>99220</v>
+        <v>99221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54650-2022 artfynd.xlsx
+++ b/artfynd/A 54650-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3191643</v>
       </c>
       <c r="B2" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2762594</v>
       </c>
       <c r="B3" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2330905</v>
       </c>
       <c r="B4" t="n">
-        <v>107297</v>
+        <v>107325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4690495</v>
       </c>
       <c r="B5" t="n">
-        <v>99221</v>
+        <v>99248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54650-2022 artfynd.xlsx
+++ b/artfynd/A 54650-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3191643</v>
       </c>
       <c r="B2" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2762594</v>
       </c>
       <c r="B3" t="n">
-        <v>109477</v>
+        <v>109483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2330905</v>
       </c>
       <c r="B4" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4690495</v>
       </c>
       <c r="B5" t="n">
-        <v>99248</v>
+        <v>99254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54650-2022 artfynd.xlsx
+++ b/artfynd/A 54650-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3191643</v>
       </c>
       <c r="B2" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2762594</v>
       </c>
       <c r="B3" t="n">
-        <v>109483</v>
+        <v>109490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2330905</v>
       </c>
       <c r="B4" t="n">
-        <v>107331</v>
+        <v>107338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4690495</v>
       </c>
       <c r="B5" t="n">
-        <v>99254</v>
+        <v>99261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54650-2022 artfynd.xlsx
+++ b/artfynd/A 54650-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3191643</v>
       </c>
       <c r="B2" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2762594</v>
       </c>
       <c r="B3" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2330905</v>
       </c>
       <c r="B4" t="n">
-        <v>107338</v>
+        <v>107342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4690495</v>
       </c>
       <c r="B5" t="n">
-        <v>99261</v>
+        <v>99265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54650-2022 artfynd.xlsx
+++ b/artfynd/A 54650-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3191643</v>
       </c>
       <c r="B2" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2762594</v>
       </c>
       <c r="B3" t="n">
-        <v>109494</v>
+        <v>109502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2330905</v>
       </c>
       <c r="B4" t="n">
-        <v>107342</v>
+        <v>107350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4690495</v>
       </c>
       <c r="B5" t="n">
-        <v>99265</v>
+        <v>99272</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
